--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_361_R37.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_361_R37.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Q. ELLIS</t>
+          <t>S. SHIELDS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.682</v>
+        <v>3.0771</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6053</v>
+        <v>2.5998</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0767</v>
+        <v>0.4773</v>
       </c>
       <c r="G2" t="n">
-        <v>1.5821</v>
+        <v>0.8902</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4383</v>
+        <v>-0.4382</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1438</v>
+        <v>1.3284</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6268</v>
+        <v>3.0527</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2183</v>
+        <v>0.1953</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4085</v>
+        <v>2.8573</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.0447</v>
+        <v>-2.1625</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.78</v>
+        <v>-0.6335</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.2647</v>
+        <v>-1.529</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.5515</v>
+        <v>-1.3917</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9278</v>
+        <v>2.0876</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5818</v>
+        <v>0.0246</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3882</v>
+        <v>-0.1333</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1936</v>
+        <v>0.1579</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1418</v>
+        <v>1.4665</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. SHIELDS</t>
+          <t>D. BOOKER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5223</v>
+        <v>2.4609</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4819</v>
+        <v>1.5426</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0404</v>
+        <v>0.9183</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8902</v>
+        <v>1.3638</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4382</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3284</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0527</v>
+        <v>1.4674</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1953</v>
+        <v>0.3767</v>
       </c>
       <c r="L3" t="n">
-        <v>2.8573</v>
+        <v>1.0907</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.1625</v>
+        <v>-0.1036</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6335</v>
+        <v>0.3748</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.529</v>
+        <v>-0.4783</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5302</v>
+        <v>-0.2045</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2513</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2789</v>
+        <v>-0.1379</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4665</v>
+        <v>0.1418</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8511</v>
+        <v>1.8249</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6775</v>
+        <v>1.7522</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1736</v>
+        <v>0.0727</v>
       </c>
       <c r="G4" t="n">
         <v>1.0785</v>
@@ -766,13 +766,13 @@
         <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3809</v>
+        <v>0.3547</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2715</v>
+        <v>0.3462</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1094</v>
+        <v>0.0086</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5361</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. BOOKER</t>
+          <t>Q. ELLIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7964</v>
+        <v>1.4359</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8782</v>
+        <v>1.6617</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9183</v>
+        <v>-0.2258</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3638</v>
+        <v>1.5821</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7514999999999999</v>
+        <v>1.4383</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.1438</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4674</v>
+        <v>3.6268</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3767</v>
+        <v>2.2183</v>
       </c>
       <c r="L5" t="n">
-        <v>1.0907</v>
+        <v>1.4085</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1036</v>
+        <v>-2.0447</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3748</v>
+        <v>-0.78</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4783</v>
+        <v>-1.2647</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1598</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8689</v>
+        <v>1.3357</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.731</v>
+        <v>0.4446</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1379</v>
+        <v>0.8911</v>
       </c>
       <c r="V5" t="n">
         <v>0.1418</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6889</v>
+        <v>0.1244</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4878</v>
+        <v>1.3265</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7988</v>
+        <v>-1.2021</v>
       </c>
       <c r="G6" t="n">
         <v>-0.3326</v>
@@ -922,13 +922,13 @@
         <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>0.702</v>
+        <v>0.1375</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2047</v>
+        <v>0.0435</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4973</v>
+        <v>0.094</v>
       </c>
       <c r="V6" t="n">
         <v>-1.0722</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. BOLMARO</t>
+          <t>Z. LEDAY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3797</v>
+        <v>-1.3277</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9263</v>
+        <v>-0.9901</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4534</v>
+        <v>-0.3376</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1201</v>
+        <v>-2.5263</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1141</v>
+        <v>-1.3986</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2343</v>
+        <v>-1.1276</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3274</v>
+        <v>-0.7782</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1744</v>
+        <v>-0.4937</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5018</v>
+        <v>-0.2845</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2073</v>
+        <v>-1.7481</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0602</v>
+        <v>-0.9049</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2676</v>
+        <v>-0.8431</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3195</v>
+        <v>-0.232</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3378</v>
+        <v>-0.0334</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0657</v>
+        <v>-0.1217</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7279</v>
+        <v>0.0883</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0.5361</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Z. LEDAY</t>
+          <t>M. GUDURIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4279</v>
+        <v>-1.4779</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7542</v>
+        <v>0.8127</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6737</v>
+        <v>-2.2906</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.5263</v>
+        <v>-0.5669</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3986</v>
+        <v>0.0254</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1276</v>
+        <v>-0.5923</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7782</v>
+        <v>2.3496</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4937</v>
+        <v>0.9411</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2845</v>
+        <v>1.4085</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7481</v>
+        <v>-2.9165</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9049</v>
+        <v>-0.9157</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8431</v>
+        <v>-2.0008</v>
       </c>
       <c r="P8" t="n">
+        <v>-0.6959</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-1.3917</v>
+      </c>
+      <c r="R8" t="n">
         <v>0.6959</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-0.232</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.9278</v>
-      </c>
       <c r="S8" t="n">
-        <v>-0.1336</v>
+        <v>0.6045</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1142</v>
+        <v>-0.1452</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2478</v>
+        <v>0.7497</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5361</v>
+        <v>-0.8197</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3943</v>
+        <v>-0.8197</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9187</v>
+        <v>-1.6999</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2092</v>
+        <v>-0.0912</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7095</v>
+        <v>-1.6087</v>
       </c>
       <c r="G9" t="n">
         <v>-0.9295</v>
@@ -1156,13 +1156,13 @@
         <v>0.232</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1489</v>
+        <v>0.0698</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2161</v>
+        <v>-0.0982</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0672</v>
+        <v>0.168</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0722</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. GUDURIC</t>
+          <t>L. BOLMARO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.27</v>
+        <v>-1.7775</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.013</v>
+        <v>-1.5594</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.257</v>
+        <v>-0.2181</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5669</v>
+        <v>0.1201</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0254</v>
+        <v>-0.1141</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5923</v>
+        <v>0.2343</v>
       </c>
       <c r="J10" t="n">
-        <v>2.3496</v>
+        <v>0.3274</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9411</v>
+        <v>-0.1744</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4085</v>
+        <v>0.5018</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.9165</v>
+        <v>-0.2073</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9157</v>
+        <v>0.0602</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.0008</v>
+        <v>-0.2676</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6959</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.3917</v>
+        <v>-2.3195</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1876</v>
+        <v>-0.06</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9709</v>
+        <v>0.4327</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7833</v>
+        <v>-0.4927</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.8197</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.8197</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9551</v>
+        <v>-3.8132</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0339</v>
+        <v>-1.9593</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9211</v>
+        <v>-1.8539</v>
       </c>
       <c r="G11" t="n">
         <v>-2.0053</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2539</v>
+        <v>-0.112</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1415</v>
+        <v>-0.0668</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1125</v>
+        <v>-0.0452</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5361</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.0569</v>
+        <v>-4.9211</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2581</v>
+        <v>-2.7863</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7988</v>
+        <v>-2.1349</v>
       </c>
       <c r="G12" t="n">
         <v>-2.7137</v>
@@ -1390,13 +1390,13 @@
         <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4402</v>
+        <v>0.5759</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6721</v>
+        <v>-0.2003</v>
       </c>
       <c r="U12" t="n">
-        <v>1.1123</v>
+        <v>0.7762</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.467599999999999</v>
+        <v>-6.0941</v>
       </c>
       <c r="E13" t="n">
-        <v>1.935999999999999</v>
+        <v>2.3092</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.4033</v>
+        <v>-8.403400000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-4.0396</v>
@@ -1447,7 +1447,7 @@
         <v>4.2235</v>
       </c>
       <c r="L13" t="n">
-        <v>6.088400000000001</v>
+        <v>6.0884</v>
       </c>
       <c r="M13" t="n">
         <v>-14.3516</v>
@@ -1468,13 +1468,13 @@
         <v>10.438</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3196</v>
+        <v>2.6928</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0613999999999999</v>
+        <v>0.4349</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2581</v>
+        <v>2.258</v>
       </c>
       <c r="V13" t="n">
         <v>-2.428</v>
@@ -1483,7 +1483,7 @@
         <v>4.319900000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.7479</v>
+        <v>-6.747900000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.1827</v>
+        <v>4.6158</v>
       </c>
       <c r="E14" t="n">
-        <v>2.469</v>
+        <v>2.8229</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7137</v>
+        <v>1.793</v>
       </c>
       <c r="G14" t="n">
         <v>3.2396</v>
@@ -1546,13 +1546,13 @@
         <v>0.9278</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3457</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6563</v>
+        <v>-0.3025</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3106</v>
+        <v>0.3899</v>
       </c>
       <c r="V14" t="n">
         <v>2.6805</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5312</v>
+        <v>4.2775</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0945</v>
+        <v>3.4483</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4367</v>
+        <v>0.8292</v>
       </c>
       <c r="G15" t="n">
         <v>3.2942</v>
@@ -1624,13 +1624,13 @@
         <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.995</v>
+        <v>-0.2486</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0297</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0347</v>
+        <v>0.4272</v>
       </c>
       <c r="V15" t="n">
         <v>0.5361</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2436</v>
+        <v>3.2106</v>
       </c>
       <c r="E16" t="n">
-        <v>3.7243</v>
+        <v>3.9602</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4807</v>
+        <v>-0.7496</v>
       </c>
       <c r="G16" t="n">
         <v>-1.8782</v>
@@ -1702,13 +1702,13 @@
         <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.203</v>
+        <v>-0.2359</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5737</v>
+        <v>-0.3378</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3708</v>
+        <v>0.1019</v>
       </c>
       <c r="V16" t="n">
         <v>3.4691</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.0906</v>
+        <v>2.7139</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4395</v>
+        <v>1.6138</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6511</v>
+        <v>1.1</v>
       </c>
       <c r="G17" t="n">
         <v>2.5209</v>
@@ -1780,13 +1780,13 @@
         <v>0.6959</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8918</v>
+        <v>0.5151</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1404</v>
+        <v>0.3148</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2486</v>
+        <v>0.2003</v>
       </c>
       <c r="V17" t="n">
         <v>0.1418</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8678</v>
+        <v>1.143</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1169</v>
+        <v>0.0011</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9846</v>
+        <v>1.1419</v>
       </c>
       <c r="G18" t="n">
         <v>1.3605</v>
@@ -1858,13 +1858,13 @@
         <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7943</v>
+        <v>-0.519</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8136</v>
+        <v>-0.6956</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0193</v>
+        <v>0.1766</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3943</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0599</v>
+        <v>0.8716</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3397</v>
+        <v>0.1321</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2797</v>
+        <v>0.7393999999999999</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0351</v>
@@ -1936,13 +1936,13 @@
         <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2568</v>
+        <v>-0.3253</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.731</v>
+        <v>-0.2592</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5258</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="V19" t="n">
         <v>1.0722</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3623</v>
+        <v>-1.0814</v>
       </c>
       <c r="E20" t="n">
-        <v>4.3838</v>
+        <v>3.4402</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.746</v>
+        <v>-4.5216</v>
       </c>
       <c r="G20" t="n">
         <v>0.1539</v>
@@ -2014,13 +2014,13 @@
         <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8628</v>
+        <v>0.1436</v>
       </c>
       <c r="T20" t="n">
-        <v>1.447</v>
+        <v>0.5034</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5843</v>
+        <v>-0.3598</v>
       </c>
       <c r="V20" t="n">
         <v>-2.5387</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.508</v>
+        <v>-2.2385</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.1479</v>
+        <v>-3.912</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6399</v>
+        <v>1.6735</v>
       </c>
       <c r="G21" t="n">
         <v>-1.8267</v>
@@ -2092,13 +2092,13 @@
         <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2175</v>
+        <v>0.0521</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5895</v>
+        <v>-0.3536</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3721</v>
+        <v>0.4057</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. HOLLATZ</t>
+          <t>N. GIFFEY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6776</v>
+        <v>-2.4073</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7547</v>
+        <v>-0.9946</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9228</v>
+        <v>-1.4127</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.2612</v>
+        <v>-0.5285</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.3048</v>
+        <v>0.3481</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0436</v>
+        <v>-0.8767</v>
       </c>
       <c r="J22" t="n">
-        <v>1.2981</v>
+        <v>0.3183</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.06370000000000001</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>1.3618</v>
+        <v>0.2308</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.5592</v>
+        <v>-0.8468</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.241</v>
+        <v>0.2606</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3182</v>
+        <v>-1.1074</v>
       </c>
       <c r="P22" t="n">
         <v>-0.4639</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8556</v>
+        <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1639</v>
+        <v>0.3352</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0553</v>
+        <v>-0.1531</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2192</v>
+        <v>0.4883</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.7886</v>
+        <v>-1.7501</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.7886</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>N. GIFFEY</t>
+          <t>J. HOLLATZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8405</v>
+        <v>-3.065</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3484</v>
+        <v>-2.1086</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.492</v>
+        <v>-0.9564</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5285</v>
+        <v>-1.2612</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3481</v>
+        <v>-1.3048</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8767</v>
+        <v>0.0436</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3183</v>
+        <v>1.2981</v>
       </c>
       <c r="K23" t="n">
-        <v>0.08749999999999999</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2308</v>
+        <v>1.3618</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8468</v>
+        <v>-2.5592</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2606</v>
+        <v>-1.241</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.1074</v>
+        <v>-1.3182</v>
       </c>
       <c r="P23" t="n">
         <v>-0.4639</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.098</v>
+        <v>-0.5513</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.507</v>
+        <v>-0.2985</v>
       </c>
       <c r="U23" t="n">
-        <v>0.409</v>
+        <v>-0.2528</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.7501</v>
+        <v>-0.7886</v>
       </c>
       <c r="W23" t="n">
+        <v>-0.7886</v>
+      </c>
+      <c r="X23" t="n">
         <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>-1.7501</v>
       </c>
     </row>
     <row r="24">
@@ -2281,22 +2281,22 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>6.467599999999997</v>
+        <v>8.0402</v>
       </c>
       <c r="E24" t="n">
-        <v>8.403499999999999</v>
+        <v>8.403400000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.935800000000001</v>
+        <v>-0.3633000000000007</v>
       </c>
       <c r="G24" t="n">
-        <v>4.039399999999998</v>
+        <v>4.039399999999999</v>
       </c>
       <c r="H24" t="n">
         <v>0.8940000000000003</v>
       </c>
       <c r="I24" t="n">
-        <v>3.145399999999999</v>
+        <v>3.1454</v>
       </c>
       <c r="J24" t="n">
         <v>14.3515</v>
@@ -2326,13 +2326,13 @@
         <v>12.7575</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.319599999999999</v>
+        <v>-0.7467000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.2581</v>
+        <v>-2.258</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.06140000000000012</v>
+        <v>1.5112</v>
       </c>
       <c r="V24" t="n">
         <v>2.428</v>
